--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.79556738293282</v>
+        <v>2.079279699726583</v>
       </c>
       <c r="D2" t="n">
-        <v>6.595744011311788</v>
+        <v>1.071808401838166</v>
       </c>
       <c r="E2" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F2" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5356657621233</v>
+        <v>4.474545686345037</v>
       </c>
       <c r="D3" t="n">
-        <v>14.6122239797086</v>
+        <v>2.374486396702648</v>
       </c>
       <c r="E3" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F3" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.639938717807826</v>
+        <v>1.566490041643772</v>
       </c>
       <c r="D4" t="n">
-        <v>9.113532585329155</v>
+        <v>1.480949045115988</v>
       </c>
       <c r="E4" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F4" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.14579875372928</v>
+        <v>4.248692297481008</v>
       </c>
       <c r="D5" t="n">
-        <v>26.76985617433555</v>
+        <v>4.350101628329528</v>
       </c>
       <c r="E5" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F5" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.90912087104156</v>
+        <v>4.210232141544253</v>
       </c>
       <c r="D6" t="n">
-        <v>20.6747607979726</v>
+        <v>3.359648629670548</v>
       </c>
       <c r="E6" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F6" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.83417546434353</v>
+        <v>6.798053512955824</v>
       </c>
       <c r="D7" t="n">
-        <v>39.72162367266991</v>
+        <v>6.45476384680886</v>
       </c>
       <c r="E7" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F7" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.16266325378048</v>
+        <v>6.526432778739328</v>
       </c>
       <c r="D8" t="n">
-        <v>14.50303785872015</v>
+        <v>2.356743652042025</v>
       </c>
       <c r="E8" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F8" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.55486841690293</v>
+        <v>3.177666117746726</v>
       </c>
       <c r="D9" t="n">
-        <v>44.62938976158313</v>
+        <v>7.25227583625726</v>
       </c>
       <c r="E9" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F9" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>57.79760899996691</v>
+        <v>9.392111462494624</v>
       </c>
       <c r="D10" t="n">
-        <v>16.3290599908156</v>
+        <v>2.653472248507535</v>
       </c>
       <c r="E10" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F10" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>56.85343015326202</v>
+        <v>9.238682399905079</v>
       </c>
       <c r="D11" t="n">
-        <v>20.30326561630315</v>
+        <v>3.299280662649262</v>
       </c>
       <c r="E11" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F11" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>55.85322877014124</v>
+        <v>9.076149675147951</v>
       </c>
       <c r="D12" t="n">
-        <v>38.2554928187896</v>
+        <v>6.21651758305331</v>
       </c>
       <c r="E12" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F12" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>52.25321780472682</v>
+        <v>8.49114789326811</v>
       </c>
       <c r="D13" t="n">
-        <v>44.95027351499147</v>
+        <v>7.304419446186115</v>
       </c>
       <c r="E13" t="n">
-        <v>16.81102646214553</v>
+        <v>2.731791800098649</v>
       </c>
       <c r="F13" t="n">
-        <v>13.23816613866155</v>
+        <v>2.151201997532502</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
